--- a/out/MLP-mamba2_repeat_5_000005.xlsx
+++ b/out/MLP-mamba2_repeat_5_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.443559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.443559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.443559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.443559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.443559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.443559541701984</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.043559541701984</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.043559541701984</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.443559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.043559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.443559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8241370729394373</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.443559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.043559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.043559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8241370729394373</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8241370729394373</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.043559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.043559541701984</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.043559541701984</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.043559541701984</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.043559541701984</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.043559541701984</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.043559541701984</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_5_000005.xlsx
+++ b/out/MLP-mamba2_repeat_5_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242511</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242511</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.443559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.043559541701984</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242511</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242523</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242521</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.043559541701984</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.043559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_5_000005.xlsx
+++ b/out/MLP-mamba2_repeat_5_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.420417457818985</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4424866139888763</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.65</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.7290830016136169</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5239807367324829</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7001101738204645</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3891671895980835</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7001101738204644</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5424252152442932</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.7512407302856445</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2092209309339523</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.044636661902425</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.3701752722263336</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2361792176961899</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.507626473903656</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2757899165153503</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.3620840311050415</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2776452898979187</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2870543897151947</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.7525256872177124</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.638856828212738</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.355583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.8546567559242249</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4244928956031799</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.7924069166183472</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.04463666190242511</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3202957212924957</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.04463666190242511</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.2025042623281479</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3372996151447296</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6574112176895142</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4817888140678406</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.2793282866477966</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6163904070854187</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3721857368946075</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3971255719661713</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5723705887794495</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.8948146104812622</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3408411741256714</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.1555663496255875</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5033527016639709</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3635270297527313</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.1240958720445633</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6298959851264954</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5163918733596802</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2370785176753998</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5358145833015442</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.04463666190242505</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.3776113092899323</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.04463666190242505</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.4125627279281616</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>0.3466795384883881</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.2963401675224304</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.505940318107605</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.3514252007007599</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4173335433006287</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3373171389102936</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.2969211935997009</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3873308002948761</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.16</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.578457772731781</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.04463666190242505</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4661910831928253</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.04463666190242505</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.316381424665451</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.044636661902425</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5813451409339905</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.2784609794616699</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.7182735800743103</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.04463666190242511</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2840364277362823</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5497433543205261</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.5404214859008789</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7001101738204644</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2894919812679291</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.04463666190242516</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.2429304718971252</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3712663948535919</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3764618933200836</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3719393312931061</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3688437640666962</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4843698740005493</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3513577282428741</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3281983137130737</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3827303349971771</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2565155327320099</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1531724631786346</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1496571898460388</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.04463666190242523</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7790021300315857</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.04463666190242521</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3272432684898376</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.6982613205909729</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.5734663009643555</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.355583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5062032341957092</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.385315328836441</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3889427781105042</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5024686455726624</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3027712106704712</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6967610120773315</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.458347499370575</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5001101738204644</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.6941803693771362</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4289657473564148</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.6823384165763855</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7670186161994934</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6797776222229004</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2234884649515152</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.04463666190242516</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2698499858379364</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4329908192157745</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3297155797481537</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6195803284645081</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.5018311738967896</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7531171441078186</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3362827897071838</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3717682361602783</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4450225830078125</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4584434926509857</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2624836564064026</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.7590541243553162</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3897870182991028</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5060535073280334</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.6220906972885132</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4023208916187286</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.044636661902425</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4223318696022034</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.331606388092041</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3259516358375549</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3655912578105927</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2982096076011658</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3217738270759583</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3368843793869019</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.831658661365509</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.044636661902425</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.2975777387619019</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.8577849268913269</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.5258544683456421</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.6302216053009033</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5274224877357483</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.5596067309379578</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.6274715662002563</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.8911759257316589</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.7166070342063904</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.8022816777229309</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.2168556451797485</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.417463481426239</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_5_000005.xlsx
+++ b/out/MLP-mamba2_repeat_5_000005.xlsx
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.3701752722263336</v>
+        <v>0.370175302028656</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2361792176961899</v>
+        <v>0.2361792773008347</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2870543897151947</v>
+        <v>0.2870544493198395</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.7525256872177124</v>
+        <v>0.7525256276130676</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3971255719661713</v>
+        <v>0.3971256017684937</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3408411741256714</v>
+        <v>0.340841144323349</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.1555663496255875</v>
+        <v>0.1555663645267487</v>
       </c>
       <c r="JB34" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.3635270297527313</v>
+        <v>0.3635270595550537</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.1240958720445633</v>
+        <v>0.1240959018468857</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.1600000000000001</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.6298959851264954</v>
+        <v>0.6298961043357849</v>
       </c>
       <c r="JB38" t="n">
         <v>0.1600000000000001</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.2370785176753998</v>
+        <v>0.2370785772800446</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.3776113092899323</v>
+        <v>0.3776112496852875</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.3466795384883881</v>
+        <v>0.3466795682907104</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.3514252007007599</v>
+        <v>0.3514252305030823</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.3373171389102936</v>
+        <v>0.3373171985149384</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.2969211935997009</v>
+        <v>0.2969211637973785</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.3873308002948761</v>
+        <v>0.3873308300971985</v>
       </c>
       <c r="JB51" t="n">
         <v>0.16</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.316381424665451</v>
+        <v>0.3163814544677734</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.2840364277362823</v>
+        <v>0.2840364575386047</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.5404214859008789</v>
+        <v>0.5404215455055237</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.5799999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.2894919812679291</v>
+        <v>0.2894920110702515</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.5799999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3712663948535919</v>
+        <v>0.3712663650512695</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3764618933200836</v>
+        <v>0.376461923122406</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3719393312931061</v>
+        <v>0.3719393610954285</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3513577282428741</v>
+        <v>0.3513577878475189</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.3281983137130737</v>
+        <v>0.3281983435153961</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3827303349971771</v>
+        <v>0.3827303051948547</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2565155327320099</v>
+        <v>0.2565155625343323</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1531724631786346</v>
+        <v>0.1531724482774734</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3272432684898376</v>
+        <v>0.3272432386875153</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.5734663009643555</v>
+        <v>0.5734662413597107</v>
       </c>
       <c r="JB77" t="n">
         <v>0.4399999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.5062032341957092</v>
+        <v>0.5062031745910645</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.385315328836441</v>
+        <v>0.3853152096271515</v>
       </c>
       <c r="JB79" t="n">
         <v>0.3</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.3889427781105042</v>
+        <v>0.3889427483081818</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5024686455726624</v>
+        <v>0.5024685859680176</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6967610120773315</v>
+        <v>0.6967609524726868</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.6941803693771362</v>
+        <v>0.6941803097724915</v>
       </c>
       <c r="JB85" t="n">
         <v>0.8599999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.6823384165763855</v>
+        <v>0.6823383569717407</v>
       </c>
       <c r="JB87" t="n">
         <v>0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7670186161994934</v>
+        <v>0.7670185565948486</v>
       </c>
       <c r="JB88" t="n">
         <v>0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.6797776222229004</v>
+        <v>0.6797775626182556</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2234884649515152</v>
+        <v>0.2234884798526764</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.2698499858379364</v>
+        <v>0.269849956035614</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4329908192157745</v>
+        <v>0.4329909086227417</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.8599999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3297155797481537</v>
+        <v>0.3297155499458313</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.3362827897071838</v>
+        <v>0.3362827599048615</v>
       </c>
       <c r="JB97" t="n">
         <v>0.16</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3717682361602783</v>
+        <v>0.3717682659626007</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.2624836564064026</v>
+        <v>0.2624835968017578</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3897870182991028</v>
+        <v>0.3897869884967804</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.6220906972885132</v>
+        <v>0.6220906376838684</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4023208916187286</v>
+        <v>0.4023209810256958</v>
       </c>
       <c r="JB106" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.4223318696022034</v>
+        <v>0.4223318994045258</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.1199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.3259516358375549</v>
+        <v>0.3259516060352325</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3655912578105927</v>
+        <v>0.3655912280082703</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2982096076011658</v>
+        <v>0.298209547996521</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.3217738270759583</v>
+        <v>0.3217738568782806</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.2975777387619019</v>
+        <v>0.2975776791572571</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.8577849268913269</v>
+        <v>0.8577843904495239</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.6302216053009033</v>
+        <v>0.6302214860916138</v>
       </c>
       <c r="JB118" t="n">
         <v>0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.5274224877357483</v>
+        <v>0.5274225473403931</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.7166070342063904</v>
+        <v>0.7166070938110352</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.2168556451797485</v>
+        <v>0.2168556898832321</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5800000000000005</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.417463481426239</v>
+        <v>0.4174635112285614</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.000000000000001</v>
